--- a/hotel_manager_forms/007_hotel_rfp_form_template--hotel_manager_forms.xlsx
+++ b/hotel_manager_forms/007_hotel_rfp_form_template--hotel_manager_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_1</t>
+          <t>hotel_details_form</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_2</t>
+          <t>sales_form</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_3</t>
+          <t>revenue_form</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_4</t>
+          <t>event_form</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_5</t>
+          <t>operations_form</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_6</t>
+          <t>contact_details_form</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Contact Details</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_7</t>
+          <t>sales_details_form</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Contact Details</t>
+          <t>Sales Details</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_8</t>
+          <t>revenue_details_form</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sales Details</t>
+          <t>Revenue Details</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_9</t>
+          <t>event_details_form</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Revenue Details</t>
+          <t>Event Details</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_details</t>
+          <t>operations_details_form</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Event Details</t>
+          <t>Operations Details</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_11</t>
+          <t>administrative_form</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Operations Details</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,35 +773,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_12</t>
+          <t>lead_time_form</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Administrative Details</t>
+          <t>Lead Time</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_13</t>
+          <t>sales_team_form</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hotel Details</t>
+          <t>Sales Team</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form_14</t>
+          <t>sales_manager_form</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sales Team</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_15</t>
+          <t>sales_channel_form</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Sales Channel</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_16</t>
+          <t>contact_person_form</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sales Channel</t>
+          <t>Contact Person</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,18 +888,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_17</t>
+          <t>contact_number_form</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lead Time</t>
+          <t>Contact Number</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>form_18</t>
+          <t>email_form</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Contact Person</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_19</t>
+          <t>sales_channel_form_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Sales Channel Form 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,131 +957,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_20</t>
+          <t>lead_time_form_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Lead Time Form 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>form_21</t>
+          <t>additional_notes_form</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sales Channel</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Lead Time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>form_23</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>form_24</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>form_25</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +1006,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,92 +1034,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_14_choices</t>
+          <t>sales_team_form_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>sales_team</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Sales Team</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_14_choices</t>
+          <t>sales_team_form_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>marketing_team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Marketing Team</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_14_choices</t>
+          <t>sales_team_form_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>revenue_team</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Revenue Team</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_14_choices</t>
+          <t>sales_team_form_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>operations_team</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Operations Team</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_14_choices</t>
+          <t>sales_team_form_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>admin_team</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Admin Team</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_15_choices</t>
+          <t>sales_manager_form_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1136,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_15_choices</t>
+          <t>sales_manager_form_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1153,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_15_choices</t>
+          <t>sales_manager_form_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1170,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_15_choices</t>
+          <t>sales_manager_form_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,185 +1187,168 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_15_choices</t>
+          <t>sales_channel_form_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_16_choices</t>
+          <t>sales_channel_form_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_16_choices</t>
+          <t>sales_channel_form_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_16_choices</t>
+          <t>sales_channel_form_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_16_choices</t>
+          <t>sales_channel_form_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>in-person</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>In-person</t>
+          <t>Web</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_16_choices</t>
+          <t>sales_channel_form_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_21_choices</t>
+          <t>sales_channel_form_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>form_21_choices</t>
+          <t>sales_channel_form_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>form_21_choices</t>
+          <t>sales_channel_form_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>form_21_choices</t>
+          <t>sales_channel_form_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>in-person</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>form_21_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
